--- a/data/research/model_ledgers/npb-tie-aware-elo.xlsx
+++ b/data/research/model_ledgers/npb-tie-aware-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ3"/>
+  <dimension ref="A1:AJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -872,8 +872,926 @@
       <c r="AI3" s="2" t="inlineStr"/>
       <c r="AJ3" s="2" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>9718465a25c741ca</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6d6669d47bc91bfec82db00ad3cb5bea565b364709e20a7346cef2b95011e4a9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>68272</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0.524037</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>-0.09573486311787072</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:17:38.867915Z</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:45:00Z</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AG4" s="2" t="inlineStr"/>
+      <c r="AH4" s="2" t="inlineStr"/>
+      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>5d1717a623364a7e</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6d6669d47bc91bfec82db00ad3cb5bea565b364709e20a7346cef2b95011e4a9</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>68273</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0.596977</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>-0.01239800000000002</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:17:39.390234Z</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>f58de675ac8a4104</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6d6669d47bc91bfec82db00ad3cb5bea565b364709e20a7346cef2b95011e4a9</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>68274</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0.545695</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>0.05549892156862751</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:17:39.965139Z</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>41b21f4a349643bc</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6d6669d47bc91bfec82db00ad3cb5bea565b364709e20a7346cef2b95011e4a9</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>68275</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0.528517</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>-0.06164693442622948</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:17:40.620587Z</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>bfd7d7fa4c5c4ba9</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6d6669d47bc91bfec82db00ad3cb5bea565b364709e20a7346cef2b95011e4a9</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>68276</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0.579364</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>-0.000467932773109192</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:17:41.271345Z</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>c8a33c7c0a054726</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>bc4fda3fccd78fdc3bca8f7cc4fb910c9fcb1d51c5557416c7b46467f043e355</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>68273</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0.596977</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>-0.06288694557823138</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:27.161124Z</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>fb7c483986a44c6c</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>bc4fda3fccd78fdc3bca8f7cc4fb910c9fcb1d51c5557416c7b46467f043e355</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>68274</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0.545695</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>0.06492576923076931</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:27.795687Z</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>13edee4dc6bc4cb9</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>bc4fda3fccd78fdc3bca8f7cc4fb910c9fcb1d51c5557416c7b46467f043e355</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>68275</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0.528517</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>-0.0422984506437768</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:28.470678Z</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>9d4ef8b574cf43fb</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>bc4fda3fccd78fdc3bca8f7cc4fb910c9fcb1d51c5557416c7b46467f043e355</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>68276</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0.579364</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>-0.03001100000000001</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:29.194611Z</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ3"/>
+  <autoFilter ref="A1:AJ12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/npb-tie-aware-elo.xlsx
+++ b/data/research/model_ledgers/npb-tie-aware-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ12"/>
+  <dimension ref="A1:AJ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -958,14 +958,26 @@
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
       <c r="Z4" s="2" t="inlineStr"/>
       <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:43.817847Z</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="inlineStr"/>
       <c r="AF4" s="2" t="inlineStr"/>
@@ -1468,14 +1480,26 @@
       <c r="W9" s="2" t="inlineStr"/>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="Z9" s="2" t="inlineStr"/>
       <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr"/>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>0.6443</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:43.890844Z</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
@@ -1570,14 +1594,26 @@
       <c r="W10" s="2" t="inlineStr"/>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y10" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
       <c r="Z10" s="2" t="inlineStr"/>
       <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:43.961870Z</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr"/>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -1672,14 +1708,26 @@
       <c r="W11" s="2" t="inlineStr"/>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
       <c r="Z11" s="2" t="inlineStr"/>
       <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:44.034560Z</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr"/>
       <c r="AE11" s="2" t="inlineStr"/>
       <c r="AF11" s="2" t="inlineStr"/>
@@ -1774,14 +1822,26 @@
       <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="Z12" s="2" t="inlineStr"/>
       <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr"/>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>0.8013</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:44.107133Z</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr"/>
       <c r="AE12" s="2" t="inlineStr"/>
       <c r="AF12" s="2" t="inlineStr"/>
@@ -1790,8 +1850,1232 @@
       <c r="AI12" s="2" t="inlineStr"/>
       <c r="AJ12" s="2" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>0b329c9b92074ced</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5b398d595c44a19a448f8c837e83096ca4a14ffee1657fa38933a843ff1c0f9e</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>69524</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0.512165</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>-0.08783500000000011</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:38.241715Z</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:45:00Z</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>e37c7f7aede9410a</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5b398d595c44a19a448f8c837e83096ca4a14ffee1657fa38933a843ff1c0f9e</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>69525</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0.605094</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>0.05554445045045053</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:39.041565Z</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>76a80e4d54b84664</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5b398d595c44a19a448f8c837e83096ca4a14ffee1657fa38933a843ff1c0f9e</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>69526</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0.511776</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>-0.018740431924882617</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:39.865669Z</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>f67c50e0a725475c</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5b398d595c44a19a448f8c837e83096ca4a14ffee1657fa38933a843ff1c0f9e</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>69527</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0.565314</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>-0.05445786311787071</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:40.783162Z</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr"/>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>dce6be9da0784202</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5b398d595c44a19a448f8c837e83096ca4a14ffee1657fa38933a843ff1c0f9e</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>69528</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0.587499</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>-0.002664934426229504</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:41.687478Z</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="inlineStr"/>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr"/>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>af8bf206db7c4c0d</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5b398d595c44a19a448f8c837e83096ca4a14ffee1657fa38933a843ff1c0f9e</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>69529</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0.532673</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>-0.026798365638766586</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:42.519235Z</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>11c1bbba4af44895</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>69524</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0.512165</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>-0.08783500000000011</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:49.025090Z</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:45:00Z</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="inlineStr"/>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ce74c7a2064045bd</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>69525</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0.605094</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>0.05554445045045053</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:49.865696Z</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AG20" s="2" t="inlineStr"/>
+      <c r="AH20" s="2" t="inlineStr"/>
+      <c r="AI20" s="2" t="inlineStr"/>
+      <c r="AJ20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2e24f38a3f5240dd</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>69526</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0.511776</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>-0.018740431924882617</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:50.743012Z</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>8948b11d9445497a</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>69527</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0.565314</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>-0.06431562962962956</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:51.558960Z</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr"/>
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>f5797a8ebb174996</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>69528</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0.587499</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>-0.002664934426229504</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:52.448253Z</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr"/>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr"/>
+      <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AG23" s="2" t="inlineStr"/>
+      <c r="AH23" s="2" t="inlineStr"/>
+      <c r="AI23" s="2" t="inlineStr"/>
+      <c r="AJ23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>8be3441abdeb458e</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>69529</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0.532673</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>-0.026798365638766586</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:53.416071Z</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr"/>
+      <c r="AE24" s="2" t="inlineStr"/>
+      <c r="AF24" s="2" t="inlineStr"/>
+      <c r="AG24" s="2" t="inlineStr"/>
+      <c r="AH24" s="2" t="inlineStr"/>
+      <c r="AI24" s="2" t="inlineStr"/>
+      <c r="AJ24" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ12"/>
+  <autoFilter ref="A1:AJ24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/npb-tie-aware-elo.xlsx
+++ b/data/research/model_ledgers/npb-tie-aware-elo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ24"/>
+  <dimension ref="A1:AJ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2548,14 +2548,26 @@
       <c r="W19" s="2" t="inlineStr"/>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y19" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
       <c r="Z19" s="2" t="inlineStr"/>
       <c r="AA19" s="2" t="inlineStr"/>
-      <c r="AB19" s="2" t="inlineStr"/>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:18.652697Z</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr"/>
       <c r="AE19" s="2" t="inlineStr"/>
       <c r="AF19" s="2" t="inlineStr"/>
@@ -2650,14 +2662,26 @@
       <c r="W20" s="2" t="inlineStr"/>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y20" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="Z20" s="2" t="inlineStr"/>
       <c r="AA20" s="2" t="inlineStr"/>
-      <c r="AB20" s="2" t="inlineStr"/>
-      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>1.0246</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:18.737901Z</t>
+        </is>
+      </c>
       <c r="AD20" s="2" t="inlineStr"/>
       <c r="AE20" s="2" t="inlineStr"/>
       <c r="AF20" s="2" t="inlineStr"/>
@@ -2752,14 +2776,26 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y21" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
       <c r="Z21" s="2" t="inlineStr"/>
       <c r="AA21" s="2" t="inlineStr"/>
-      <c r="AB21" s="2" t="inlineStr"/>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:18.828072Z</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr"/>
       <c r="AE21" s="2" t="inlineStr"/>
       <c r="AF21" s="2" t="inlineStr"/>
@@ -2854,14 +2890,26 @@
       <c r="W22" s="2" t="inlineStr"/>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y22" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="Z22" s="2" t="inlineStr"/>
       <c r="AA22" s="2" t="inlineStr"/>
-      <c r="AB22" s="2" t="inlineStr"/>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>0.5882</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:18.913905Z</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr"/>
       <c r="AE22" s="2" t="inlineStr"/>
       <c r="AF22" s="2" t="inlineStr"/>
@@ -2956,14 +3004,26 @@
       <c r="W23" s="2" t="inlineStr"/>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y23" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="Z23" s="2" t="inlineStr"/>
       <c r="AA23" s="2" t="inlineStr"/>
-      <c r="AB23" s="2" t="inlineStr"/>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0.8681</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:19.012865Z</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr"/>
       <c r="AE23" s="2" t="inlineStr"/>
       <c r="AF23" s="2" t="inlineStr"/>
@@ -3058,14 +3118,26 @@
       <c r="W24" s="2" t="inlineStr"/>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="Z24" s="2" t="inlineStr"/>
       <c r="AA24" s="2" t="inlineStr"/>
-      <c r="AB24" s="2" t="inlineStr"/>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0.7874</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:19.141659Z</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr"/>
       <c r="AE24" s="2" t="inlineStr"/>
       <c r="AF24" s="2" t="inlineStr"/>
@@ -3074,8 +3146,620 @@
       <c r="AI24" s="2" t="inlineStr"/>
       <c r="AJ24" s="2" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>1d3a1e21e60d40cf</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>71688</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0.671883</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>0.06250800000000001</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:05.382616Z</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr"/>
+      <c r="AE25" s="2" t="inlineStr"/>
+      <c r="AF25" s="2" t="inlineStr"/>
+      <c r="AG25" s="2" t="inlineStr"/>
+      <c r="AH25" s="2" t="inlineStr"/>
+      <c r="AI25" s="2" t="inlineStr"/>
+      <c r="AJ25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>8b89792fb3ed45f7</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>71689</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0.587646</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>-0.08232099669966997</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:06.385882Z</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr"/>
+      <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AG26" s="2" t="inlineStr"/>
+      <c r="AH26" s="2" t="inlineStr"/>
+      <c r="AI26" s="2" t="inlineStr"/>
+      <c r="AJ26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>19df1da4a7d34cc4</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>71690</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0.577661</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>-0.07268865034965033</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:06.951384Z</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr"/>
+      <c r="AE27" s="2" t="inlineStr"/>
+      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AG27" s="2" t="inlineStr"/>
+      <c r="AH27" s="2" t="inlineStr"/>
+      <c r="AI27" s="2" t="inlineStr"/>
+      <c r="AJ27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>cd9a044ce0504a87</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>71691</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0.648431</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0.7198879551820728</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>-0.07145695518207285</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:07.658626Z</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr"/>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr"/>
+      <c r="AE28" s="2" t="inlineStr"/>
+      <c r="AF28" s="2" t="inlineStr"/>
+      <c r="AG28" s="2" t="inlineStr"/>
+      <c r="AH28" s="2" t="inlineStr"/>
+      <c r="AI28" s="2" t="inlineStr"/>
+      <c r="AJ28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2783f69041f94e58</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>71692</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0.57184</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>-0.028160000000000074</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:08.234637Z</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr"/>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr"/>
+      <c r="AE29" s="2" t="inlineStr"/>
+      <c r="AF29" s="2" t="inlineStr"/>
+      <c r="AG29" s="2" t="inlineStr"/>
+      <c r="AH29" s="2" t="inlineStr"/>
+      <c r="AI29" s="2" t="inlineStr"/>
+      <c r="AJ29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>8a55663399964307</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>71693</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0.55195</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>0.021433568075117426</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:08.876525Z</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr"/>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr"/>
+      <c r="AE30" s="2" t="inlineStr"/>
+      <c r="AF30" s="2" t="inlineStr"/>
+      <c r="AG30" s="2" t="inlineStr"/>
+      <c r="AH30" s="2" t="inlineStr"/>
+      <c r="AI30" s="2" t="inlineStr"/>
+      <c r="AJ30" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ24"/>
+  <autoFilter ref="A1:AJ30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/npb-tie-aware-elo.xlsx
+++ b/data/research/model_ledgers/npb-tie-aware-elo.xlsx
@@ -3232,14 +3232,26 @@
       <c r="W25" s="2" t="inlineStr"/>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y25" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
       <c r="Z25" s="2" t="inlineStr"/>
       <c r="AA25" s="2" t="inlineStr"/>
-      <c r="AB25" s="2" t="inlineStr"/>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:21.940116Z</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr"/>
       <c r="AE25" s="2" t="inlineStr"/>
       <c r="AF25" s="2" t="inlineStr"/>
@@ -3334,14 +3346,26 @@
       <c r="W26" s="2" t="inlineStr"/>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y26" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="Z26" s="2" t="inlineStr"/>
       <c r="AA26" s="2" t="inlineStr"/>
-      <c r="AB26" s="2" t="inlineStr"/>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:22.157709Z</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr"/>
       <c r="AE26" s="2" t="inlineStr"/>
       <c r="AF26" s="2" t="inlineStr"/>
@@ -3436,14 +3460,26 @@
       <c r="W27" s="2" t="inlineStr"/>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
       <c r="Z27" s="2" t="inlineStr"/>
       <c r="AA27" s="2" t="inlineStr"/>
-      <c r="AB27" s="2" t="inlineStr"/>
-      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:22.461290Z</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr"/>
       <c r="AE27" s="2" t="inlineStr"/>
       <c r="AF27" s="2" t="inlineStr"/>
@@ -3538,14 +3574,26 @@
       <c r="W28" s="2" t="inlineStr"/>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y28" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="Z28" s="2" t="inlineStr"/>
       <c r="AA28" s="2" t="inlineStr"/>
-      <c r="AB28" s="2" t="inlineStr"/>
-      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:22.683216Z</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr"/>
       <c r="AE28" s="2" t="inlineStr"/>
       <c r="AF28" s="2" t="inlineStr"/>
@@ -3640,14 +3688,26 @@
       <c r="W29" s="2" t="inlineStr"/>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y29" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="Z29" s="2" t="inlineStr"/>
       <c r="AA29" s="2" t="inlineStr"/>
-      <c r="AB29" s="2" t="inlineStr"/>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:22.906835Z</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr"/>
       <c r="AE29" s="2" t="inlineStr"/>
       <c r="AF29" s="2" t="inlineStr"/>
@@ -3742,14 +3802,26 @@
       <c r="W30" s="2" t="inlineStr"/>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y30" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
       <c r="Z30" s="2" t="inlineStr"/>
       <c r="AA30" s="2" t="inlineStr"/>
-      <c r="AB30" s="2" t="inlineStr"/>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:23.135368Z</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr"/>
       <c r="AE30" s="2" t="inlineStr"/>
       <c r="AF30" s="2" t="inlineStr"/>

--- a/data/research/model_ledgers/npb-tie-aware-elo.xlsx
+++ b/data/research/model_ledgers/npb-tie-aware-elo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ12"/>
+  <dimension ref="A1:AJ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -958,14 +958,26 @@
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
       <c r="Z4" s="2" t="inlineStr"/>
       <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:43.817847Z</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="inlineStr"/>
       <c r="AF4" s="2" t="inlineStr"/>
@@ -1468,14 +1480,26 @@
       <c r="W9" s="2" t="inlineStr"/>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="Z9" s="2" t="inlineStr"/>
       <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr"/>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>0.6443</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:43.890844Z</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
@@ -1570,14 +1594,26 @@
       <c r="W10" s="2" t="inlineStr"/>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y10" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
       <c r="Z10" s="2" t="inlineStr"/>
       <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:43.961870Z</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr"/>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -1672,14 +1708,26 @@
       <c r="W11" s="2" t="inlineStr"/>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
       <c r="Z11" s="2" t="inlineStr"/>
       <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:44.034560Z</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr"/>
       <c r="AE11" s="2" t="inlineStr"/>
       <c r="AF11" s="2" t="inlineStr"/>
@@ -1774,14 +1822,26 @@
       <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="Z12" s="2" t="inlineStr"/>
       <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr"/>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>0.8013</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:44.107133Z</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr"/>
       <c r="AE12" s="2" t="inlineStr"/>
       <c r="AF12" s="2" t="inlineStr"/>
@@ -1790,8 +1850,4352 @@
       <c r="AI12" s="2" t="inlineStr"/>
       <c r="AJ12" s="2" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>0b329c9b92074ced</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5b398d595c44a19a448f8c837e83096ca4a14ffee1657fa38933a843ff1c0f9e</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>69524</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0.512165</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>-0.08783500000000011</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:38.241715Z</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:45:00Z</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>e37c7f7aede9410a</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5b398d595c44a19a448f8c837e83096ca4a14ffee1657fa38933a843ff1c0f9e</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>69525</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0.605094</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>0.05554445045045053</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:39.041565Z</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>76a80e4d54b84664</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5b398d595c44a19a448f8c837e83096ca4a14ffee1657fa38933a843ff1c0f9e</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>69526</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0.511776</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>-0.018740431924882617</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:39.865669Z</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>f67c50e0a725475c</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5b398d595c44a19a448f8c837e83096ca4a14ffee1657fa38933a843ff1c0f9e</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>69527</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0.565314</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>-0.05445786311787071</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:40.783162Z</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr"/>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>dce6be9da0784202</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5b398d595c44a19a448f8c837e83096ca4a14ffee1657fa38933a843ff1c0f9e</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>69528</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0.587499</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>-0.002664934426229504</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:41.687478Z</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="inlineStr"/>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr"/>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>af8bf206db7c4c0d</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5b398d595c44a19a448f8c837e83096ca4a14ffee1657fa38933a843ff1c0f9e</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>69529</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0.532673</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>-0.026798365638766586</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:25:42.519235Z</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>11c1bbba4af44895</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>69524</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0.512165</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>-0.08783500000000011</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:49.025090Z</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:45:00Z</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:18.652697Z</t>
+        </is>
+      </c>
+      <c r="AD19" s="2" t="inlineStr"/>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ce74c7a2064045bd</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>69525</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0.605094</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>0.05554445045045053</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:49.865696Z</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>1.0246</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:18.737901Z</t>
+        </is>
+      </c>
+      <c r="AD20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AG20" s="2" t="inlineStr"/>
+      <c r="AH20" s="2" t="inlineStr"/>
+      <c r="AI20" s="2" t="inlineStr"/>
+      <c r="AJ20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2e24f38a3f5240dd</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>69526</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0.511776</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>-0.018740431924882617</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:50.743012Z</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:18.828072Z</t>
+        </is>
+      </c>
+      <c r="AD21" s="2" t="inlineStr"/>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>8948b11d9445497a</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>69527</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0.565314</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>-0.06431562962962956</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:51.558960Z</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>0.5882</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:18.913905Z</t>
+        </is>
+      </c>
+      <c r="AD22" s="2" t="inlineStr"/>
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>f5797a8ebb174996</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>69528</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0.587499</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>-0.002664934426229504</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:52.448253Z</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr"/>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0.8681</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:19.012865Z</t>
+        </is>
+      </c>
+      <c r="AD23" s="2" t="inlineStr"/>
+      <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AG23" s="2" t="inlineStr"/>
+      <c r="AH23" s="2" t="inlineStr"/>
+      <c r="AI23" s="2" t="inlineStr"/>
+      <c r="AJ23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>8be3441abdeb458e</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>69529</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0.532673</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>-0.026798365638766586</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:53.416071Z</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0.7874</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:19.141659Z</t>
+        </is>
+      </c>
+      <c r="AD24" s="2" t="inlineStr"/>
+      <c r="AE24" s="2" t="inlineStr"/>
+      <c r="AF24" s="2" t="inlineStr"/>
+      <c r="AG24" s="2" t="inlineStr"/>
+      <c r="AH24" s="2" t="inlineStr"/>
+      <c r="AI24" s="2" t="inlineStr"/>
+      <c r="AJ24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>1d3a1e21e60d40cf</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>71688</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0.671883</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>0.06250800000000001</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:05.382616Z</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:21.940116Z</t>
+        </is>
+      </c>
+      <c r="AD25" s="2" t="inlineStr"/>
+      <c r="AE25" s="2" t="inlineStr"/>
+      <c r="AF25" s="2" t="inlineStr"/>
+      <c r="AG25" s="2" t="inlineStr"/>
+      <c r="AH25" s="2" t="inlineStr"/>
+      <c r="AI25" s="2" t="inlineStr"/>
+      <c r="AJ25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>8b89792fb3ed45f7</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>71689</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0.587646</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>-0.08232099669966997</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:06.385882Z</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:22.157709Z</t>
+        </is>
+      </c>
+      <c r="AD26" s="2" t="inlineStr"/>
+      <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AG26" s="2" t="inlineStr"/>
+      <c r="AH26" s="2" t="inlineStr"/>
+      <c r="AI26" s="2" t="inlineStr"/>
+      <c r="AJ26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>19df1da4a7d34cc4</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>71690</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0.577661</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>-0.07268865034965033</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:06.951384Z</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:22.461290Z</t>
+        </is>
+      </c>
+      <c r="AD27" s="2" t="inlineStr"/>
+      <c r="AE27" s="2" t="inlineStr"/>
+      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AG27" s="2" t="inlineStr"/>
+      <c r="AH27" s="2" t="inlineStr"/>
+      <c r="AI27" s="2" t="inlineStr"/>
+      <c r="AJ27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>cd9a044ce0504a87</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>71691</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0.648431</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0.7198879551820728</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>-0.07145695518207285</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:07.658626Z</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr"/>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:22.683216Z</t>
+        </is>
+      </c>
+      <c r="AD28" s="2" t="inlineStr"/>
+      <c r="AE28" s="2" t="inlineStr"/>
+      <c r="AF28" s="2" t="inlineStr"/>
+      <c r="AG28" s="2" t="inlineStr"/>
+      <c r="AH28" s="2" t="inlineStr"/>
+      <c r="AI28" s="2" t="inlineStr"/>
+      <c r="AJ28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2783f69041f94e58</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>71692</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0.57184</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>-0.028160000000000074</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:08.234637Z</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr"/>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:22.906835Z</t>
+        </is>
+      </c>
+      <c r="AD29" s="2" t="inlineStr"/>
+      <c r="AE29" s="2" t="inlineStr"/>
+      <c r="AF29" s="2" t="inlineStr"/>
+      <c r="AG29" s="2" t="inlineStr"/>
+      <c r="AH29" s="2" t="inlineStr"/>
+      <c r="AI29" s="2" t="inlineStr"/>
+      <c r="AJ29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>8a55663399964307</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>71693</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0.55195</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>0.021433568075117426</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:08.876525Z</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr"/>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:23.135368Z</t>
+        </is>
+      </c>
+      <c r="AD30" s="2" t="inlineStr"/>
+      <c r="AE30" s="2" t="inlineStr"/>
+      <c r="AF30" s="2" t="inlineStr"/>
+      <c r="AG30" s="2" t="inlineStr"/>
+      <c r="AH30" s="2" t="inlineStr"/>
+      <c r="AI30" s="2" t="inlineStr"/>
+      <c r="AJ30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>737ed7173e924ec4</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>e9ab59688d3b514e2e6e6a6178916377e656c91d0946e4a0432922d92c29eca9</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>72694</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>0.654702</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>0.014414230215827328</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:06:46.964710Z</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="2" t="inlineStr"/>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:35:03.567976Z</t>
+        </is>
+      </c>
+      <c r="AD31" s="2" t="inlineStr"/>
+      <c r="AE31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr"/>
+      <c r="AG31" s="2" t="inlineStr"/>
+      <c r="AH31" s="2" t="inlineStr"/>
+      <c r="AI31" s="2" t="inlineStr"/>
+      <c r="AJ31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>918662a7048a48de</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>e9ab59688d3b514e2e6e6a6178916377e656c91d0946e4a0432922d92c29eca9</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>72695</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>0.657907</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>0.09843563436123348</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:06:47.516040Z</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr"/>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>1.3780</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:35:03.700019Z</t>
+        </is>
+      </c>
+      <c r="AD32" s="2" t="inlineStr"/>
+      <c r="AE32" s="2" t="inlineStr"/>
+      <c r="AF32" s="2" t="inlineStr"/>
+      <c r="AG32" s="2" t="inlineStr"/>
+      <c r="AH32" s="2" t="inlineStr"/>
+      <c r="AI32" s="2" t="inlineStr"/>
+      <c r="AJ32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>a51f055ab9474153</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>e9ab59688d3b514e2e6e6a6178916377e656c91d0946e4a0432922d92c29eca9</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>72735</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>0.585415</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>0.03586545045045053</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:06:48.067662Z</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr"/>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:35:03.829479Z</t>
+        </is>
+      </c>
+      <c r="AD33" s="2" t="inlineStr"/>
+      <c r="AE33" s="2" t="inlineStr"/>
+      <c r="AF33" s="2" t="inlineStr"/>
+      <c r="AG33" s="2" t="inlineStr"/>
+      <c r="AH33" s="2" t="inlineStr"/>
+      <c r="AI33" s="2" t="inlineStr"/>
+      <c r="AJ33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>64be0ccb0c6c4530</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>e9ab59688d3b514e2e6e6a6178916377e656c91d0946e4a0432922d92c29eca9</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>72736</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>0.530943</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>0.05017376923076933</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:06:48.734721Z</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr"/>
+      <c r="W34" s="2" t="inlineStr"/>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:35:03.963976Z</t>
+        </is>
+      </c>
+      <c r="AD34" s="2" t="inlineStr"/>
+      <c r="AE34" s="2" t="inlineStr"/>
+      <c r="AF34" s="2" t="inlineStr"/>
+      <c r="AG34" s="2" t="inlineStr"/>
+      <c r="AH34" s="2" t="inlineStr"/>
+      <c r="AI34" s="2" t="inlineStr"/>
+      <c r="AJ34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>efc08988d41f4f77</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>e9ab59688d3b514e2e6e6a6178916377e656c91d0946e4a0432922d92c29eca9</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>72737</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>0.564611</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>0.005139634361233436</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:06:49.378255Z</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="inlineStr"/>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:35:04.111393Z</t>
+        </is>
+      </c>
+      <c r="AD35" s="2" t="inlineStr"/>
+      <c r="AE35" s="2" t="inlineStr"/>
+      <c r="AF35" s="2" t="inlineStr"/>
+      <c r="AG35" s="2" t="inlineStr"/>
+      <c r="AH35" s="2" t="inlineStr"/>
+      <c r="AI35" s="2" t="inlineStr"/>
+      <c r="AJ35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>5ecc846d15c547b2</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>e9ab59688d3b514e2e6e6a6178916377e656c91d0946e4a0432922d92c29eca9</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>72738</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>0.596329</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>-0.003671000000000091</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:06:50.014626Z</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr"/>
+      <c r="W36" s="2" t="inlineStr"/>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:35:04.243904Z</t>
+        </is>
+      </c>
+      <c r="AD36" s="2" t="inlineStr"/>
+      <c r="AE36" s="2" t="inlineStr"/>
+      <c r="AF36" s="2" t="inlineStr"/>
+      <c r="AG36" s="2" t="inlineStr"/>
+      <c r="AH36" s="2" t="inlineStr"/>
+      <c r="AI36" s="2" t="inlineStr"/>
+      <c r="AJ36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>c2b3adb062f142c2</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>1b7c2815d24b862bd8c1893baa5e4f65c12122708fa3c5aac2d6bac9c376d736</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>73655</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>0.547003</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>0.05680692156862749</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T05:17:43.172262Z</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="inlineStr"/>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T20:26:16.445613Z</t>
+        </is>
+      </c>
+      <c r="AD37" s="2" t="inlineStr"/>
+      <c r="AE37" s="2" t="inlineStr"/>
+      <c r="AF37" s="2" t="inlineStr"/>
+      <c r="AG37" s="2" t="inlineStr"/>
+      <c r="AH37" s="2" t="inlineStr"/>
+      <c r="AI37" s="2" t="inlineStr"/>
+      <c r="AJ37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2d8fb38c37114ae7</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>1b7c2815d24b862bd8c1893baa5e4f65c12122708fa3c5aac2d6bac9c376d736</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>73656</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>0.571416</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>-0.018747934426229462</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T05:17:43.809915Z</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr"/>
+      <c r="W38" s="2" t="inlineStr"/>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T20:26:16.578793Z</t>
+        </is>
+      </c>
+      <c r="AD38" s="2" t="inlineStr"/>
+      <c r="AE38" s="2" t="inlineStr"/>
+      <c r="AF38" s="2" t="inlineStr"/>
+      <c r="AG38" s="2" t="inlineStr"/>
+      <c r="AH38" s="2" t="inlineStr"/>
+      <c r="AI38" s="2" t="inlineStr"/>
+      <c r="AJ38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>de6f8fdf77fe4e6b</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>1b7c2815d24b862bd8c1893baa5e4f65c12122708fa3c5aac2d6bac9c376d736</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>73664</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>0.604738</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>-0.004637000000000002</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T05:17:44.416064Z</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="inlineStr"/>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T20:26:16.714490Z</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr"/>
+      <c r="AE39" s="2" t="inlineStr"/>
+      <c r="AF39" s="2" t="inlineStr"/>
+      <c r="AG39" s="2" t="inlineStr"/>
+      <c r="AH39" s="2" t="inlineStr"/>
+      <c r="AI39" s="2" t="inlineStr"/>
+      <c r="AJ39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>dcd213d04264430e</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>1b7c2815d24b862bd8c1893baa5e4f65c12122708fa3c5aac2d6bac9c376d736</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>73665</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>0.540616</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>-0.0791558631178707</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T05:17:45.141880Z</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr"/>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr"/>
+      <c r="AA40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T20:26:16.850357Z</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr"/>
+      <c r="AE40" s="2" t="inlineStr"/>
+      <c r="AF40" s="2" t="inlineStr"/>
+      <c r="AG40" s="2" t="inlineStr"/>
+      <c r="AH40" s="2" t="inlineStr"/>
+      <c r="AI40" s="2" t="inlineStr"/>
+      <c r="AJ40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>d2f660c6e3d84efe</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>57711c7dd7f87479bff450e35affe6ad8204bbb79b034546650c0339ec72d351</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>76184</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>0.515505</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>0.07497636563876653</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:15:18.265822Z</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr"/>
+      <c r="W41" s="2" t="inlineStr"/>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr"/>
+      <c r="AE41" s="2" t="inlineStr"/>
+      <c r="AF41" s="2" t="inlineStr"/>
+      <c r="AG41" s="2" t="inlineStr"/>
+      <c r="AH41" s="2" t="inlineStr"/>
+      <c r="AI41" s="2" t="inlineStr"/>
+      <c r="AJ41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>32c09a5999a44072</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>57711c7dd7f87479bff450e35affe6ad8204bbb79b034546650c0339ec72d351</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>76185</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>0.53288</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>0.09235136563876656</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:15:18.944686Z</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr"/>
+      <c r="W42" s="2" t="inlineStr"/>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr"/>
+      <c r="AA42" s="2" t="inlineStr"/>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr"/>
+      <c r="AE42" s="2" t="inlineStr"/>
+      <c r="AF42" s="2" t="inlineStr"/>
+      <c r="AG42" s="2" t="inlineStr"/>
+      <c r="AH42" s="2" t="inlineStr"/>
+      <c r="AI42" s="2" t="inlineStr"/>
+      <c r="AJ42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>328f27828bcf487d</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>57711c7dd7f87479bff450e35affe6ad8204bbb79b034546650c0339ec72d351</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>76186</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>0.567846</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>-0.10212099669967001</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:15:19.707444Z</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr"/>
+      <c r="W43" s="2" t="inlineStr"/>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr"/>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr"/>
+      <c r="AE43" s="2" t="inlineStr"/>
+      <c r="AF43" s="2" t="inlineStr"/>
+      <c r="AG43" s="2" t="inlineStr"/>
+      <c r="AH43" s="2" t="inlineStr"/>
+      <c r="AI43" s="2" t="inlineStr"/>
+      <c r="AJ43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>a4ad990b948d4d4c</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>57711c7dd7f87479bff450e35affe6ad8204bbb79b034546650c0339ec72d351</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>76187</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>0.514003</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>-0.0658289327731092</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:15:20.304878Z</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr"/>
+      <c r="W44" s="2" t="inlineStr"/>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr"/>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr"/>
+      <c r="AE44" s="2" t="inlineStr"/>
+      <c r="AF44" s="2" t="inlineStr"/>
+      <c r="AG44" s="2" t="inlineStr"/>
+      <c r="AH44" s="2" t="inlineStr"/>
+      <c r="AI44" s="2" t="inlineStr"/>
+      <c r="AJ44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>a820508879db4e1f</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>57711c7dd7f87479bff450e35affe6ad8204bbb79b034546650c0339ec72d351</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>76188</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>0.654962</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>0.7101449275362319</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>-0.055182927536231885</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:15:21.027365Z</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="inlineStr"/>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr"/>
+      <c r="AE45" s="2" t="inlineStr"/>
+      <c r="AF45" s="2" t="inlineStr"/>
+      <c r="AG45" s="2" t="inlineStr"/>
+      <c r="AH45" s="2" t="inlineStr"/>
+      <c r="AI45" s="2" t="inlineStr"/>
+      <c r="AJ45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>d018cd0a2a4e4313</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>57711c7dd7f87479bff450e35affe6ad8204bbb79b034546650c0339ec72d351</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>76189</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>0.516541</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>-0.013975431924882598</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:15:21.612243Z</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr"/>
+      <c r="W46" s="2" t="inlineStr"/>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr"/>
+      <c r="AE46" s="2" t="inlineStr"/>
+      <c r="AF46" s="2" t="inlineStr"/>
+      <c r="AG46" s="2" t="inlineStr"/>
+      <c r="AH46" s="2" t="inlineStr"/>
+      <c r="AI46" s="2" t="inlineStr"/>
+      <c r="AJ46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>1d1361ae7add45aa</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>05ce5c163469a19fa69948e39f5a5c074f3e14d31fa465677897d80bd6c4e801</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>76184</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>0.515505</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>0.07497636563876653</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:31.890109Z</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr"/>
+      <c r="W47" s="2" t="inlineStr"/>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr"/>
+      <c r="Z47" s="2" t="inlineStr"/>
+      <c r="AA47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr"/>
+      <c r="AE47" s="2" t="inlineStr"/>
+      <c r="AF47" s="2" t="inlineStr"/>
+      <c r="AG47" s="2" t="inlineStr"/>
+      <c r="AH47" s="2" t="inlineStr"/>
+      <c r="AI47" s="2" t="inlineStr"/>
+      <c r="AJ47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>95a6060239644d80</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>05ce5c163469a19fa69948e39f5a5c074f3e14d31fa465677897d80bd6c4e801</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>76185</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>0.53288</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>0.09235136563876656</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:32.791156Z</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr"/>
+      <c r="W48" s="2" t="inlineStr"/>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr"/>
+      <c r="AE48" s="2" t="inlineStr"/>
+      <c r="AF48" s="2" t="inlineStr"/>
+      <c r="AG48" s="2" t="inlineStr"/>
+      <c r="AH48" s="2" t="inlineStr"/>
+      <c r="AI48" s="2" t="inlineStr"/>
+      <c r="AJ48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>002385fa0fca4316</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>05ce5c163469a19fa69948e39f5a5c074f3e14d31fa465677897d80bd6c4e801</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>76186</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>0.567846</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>-0.10212099669967001</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:33.487442Z</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr"/>
+      <c r="W49" s="2" t="inlineStr"/>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr"/>
+      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="inlineStr"/>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr"/>
+      <c r="AE49" s="2" t="inlineStr"/>
+      <c r="AF49" s="2" t="inlineStr"/>
+      <c r="AG49" s="2" t="inlineStr"/>
+      <c r="AH49" s="2" t="inlineStr"/>
+      <c r="AI49" s="2" t="inlineStr"/>
+      <c r="AJ49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>240a233d7c7546d4</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>05ce5c163469a19fa69948e39f5a5c074f3e14d31fa465677897d80bd6c4e801</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>76187</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>0.514003</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>-0.016513431924882638</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:33.970591Z</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr"/>
+      <c r="W50" s="2" t="inlineStr"/>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr"/>
+      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="inlineStr"/>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr"/>
+      <c r="AE50" s="2" t="inlineStr"/>
+      <c r="AF50" s="2" t="inlineStr"/>
+      <c r="AG50" s="2" t="inlineStr"/>
+      <c r="AH50" s="2" t="inlineStr"/>
+      <c r="AI50" s="2" t="inlineStr"/>
+      <c r="AJ50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>47fdf2f5e63145b7</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>05ce5c163469a19fa69948e39f5a5c074f3e14d31fa465677897d80bd6c4e801</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>76188</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>0.654962</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>0.7198879551820728</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>-0.06492595518207278</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:34.674761Z</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr"/>
+      <c r="W51" s="2" t="inlineStr"/>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr"/>
+      <c r="Z51" s="2" t="inlineStr"/>
+      <c r="AA51" s="2" t="inlineStr"/>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr"/>
+      <c r="AE51" s="2" t="inlineStr"/>
+      <c r="AF51" s="2" t="inlineStr"/>
+      <c r="AG51" s="2" t="inlineStr"/>
+      <c r="AH51" s="2" t="inlineStr"/>
+      <c r="AI51" s="2" t="inlineStr"/>
+      <c r="AJ51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>36e45bf075f549f1</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>05ce5c163469a19fa69948e39f5a5c074f3e14d31fa465677897d80bd6c4e801</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>76189</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>0.516541</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>-0.04293036563876651</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:35.145050Z</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr"/>
+      <c r="W52" s="2" t="inlineStr"/>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr"/>
+      <c r="Z52" s="2" t="inlineStr"/>
+      <c r="AA52" s="2" t="inlineStr"/>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr"/>
+      <c r="AE52" s="2" t="inlineStr"/>
+      <c r="AF52" s="2" t="inlineStr"/>
+      <c r="AG52" s="2" t="inlineStr"/>
+      <c r="AH52" s="2" t="inlineStr"/>
+      <c r="AI52" s="2" t="inlineStr"/>
+      <c r="AJ52" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ12"/>
+  <autoFilter ref="A1:AJ52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>